--- a/public/demo/careflow-field-outreach-demo.xlsx
+++ b/public/demo/careflow-field-outreach-demo.xlsx
@@ -1949,7 +1949,7 @@
         <v>裕安樓</v>
       </c>
       <c r="C2" t="str">
-        <v>西營盤示範街 1 號（合成）</v>
+        <v>西營盤示範街 1 號</v>
       </c>
       <c r="D2">
         <v>114.14178818464279</v>
@@ -1978,7 +1978,7 @@
         <v>海景樓</v>
       </c>
       <c r="C3" t="str">
-        <v>西營盤示範街 8 號（合成）</v>
+        <v>西營盤示範街 8 號</v>
       </c>
       <c r="D3">
         <v>114.14255797863007</v>
@@ -2007,7 +2007,7 @@
         <v>德昌樓</v>
       </c>
       <c r="C4" t="str">
-        <v>西營盤示範街 16 號（合成）</v>
+        <v>西營盤示範街 16 號</v>
       </c>
       <c r="D4">
         <v>114.14136976003647</v>
@@ -2036,7 +2036,7 @@
         <v>安和樓</v>
       </c>
       <c r="C5" t="str">
-        <v>西營盤示範街 24 號（合成）</v>
+        <v>西營盤示範街 24 號</v>
       </c>
       <c r="D5">
         <v>114.14208590984344</v>
